--- a/extenbooks/S701_extenbook.xlsx
+++ b/extenbooks/S701_extenbook.xlsx
@@ -3945,7 +3945,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -5508,11 +5508,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5535,112 +5535,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Figure 7.11 — US Selling Price vs Unit Labor Cost (cross-section), 1923–1950</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S701_research.json", "adequacy_report": "Technical/docs/chapters/CH7_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S701_DPR.md", "epr": "Technical/docs/series/S701_EPR.md", "loader": "Technical/code/L01_loaders/L01_S701_load.py", "processor": "Technical/code/P02_processors/P02_S701_construct.py", "validator": "Technical/code/V03_validators/V03_S701_validate.py", "processed": "Technical/data/processed/S701.parquet", "chopped_csv": "Technical/chopped/S701.csv", "extenbook_xlsx": "Technical/extenbooks/S701_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S701-A"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SALTER_1969_TABLE28_US"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>content_type</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>cross_sectional</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>extension_status</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>not_applicable_cross_sectional</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S701_extenbook.xlsx
+++ b/extenbooks/S701_extenbook.xlsx
@@ -3892,7 +3892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A113"/>
+  <dimension ref="A1:A136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4031,7 +4031,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>**S701** is the **cross-sectional industry scatter** that Shaikh re-plots in Fig7.11 from Salter (1969). Each point is one industry; both axes are the ratio (1950/1923 × 100; selling price and unit labour cost). Period: 1923–1950.</t>
+          <t>**S701** is the **cross-sectional industry scatter** that Shaikh re-plots in Fig7.11 from Salter (1969). Each point is one US industry; both axes are the ratio (1950/1923 × 100; selling price and unit labour cost). Period: 1923–1950. The source is **Salter 1969, p. 164, table 28**.</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>## 2. Why it matters in Chapter 7</t>
+          <t>&gt; **ERRATUM — Salter caption transposition.** The book's Fig 7.11/7.12 *captions* transpose the two Salter tables (the Fig 7.11 caption prints "Source: Salter 1969, 197, table 33"). This is a caption erratum. The authoritative mapping comes from the salvaged workbook Row-0 title ("Table 28. Changes in output per man-hour and related quantities for twenty-seven industries, United States, 1923-50 (1923 = 100)") and the book body text listing the two data sets as "(164, table 28; 197, table 33)": **US Fig 7.11 = Table 28, p.164; UK Fig 7.12 = Table 33, p.197.** Corrected 2026-07-02 (campaign DF-2); this reverses the 2026-06-11 reconciliation, which had elevated the erratum captions.</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ch7 develops Shaikh's theory of turbulent regulation of industrial profit rates by costs of production. Fig7.11 is a foundational visual demonstration that cross-industry variation in selling-price change is well explained by cross-industry variation in unit-labour-cost change (R² ≈ 0.77 per book p. 286), grounding the classical/Marxian claim that prices of production are regulated by costs.</t>
+          <t>## 2. Why it matters in Chapter 7</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>Ch7 develops Shaikh's theory of turbulent regulation of industrial profit rates by costs of production. Fig7.11 is a foundational visual demonstration that cross-industry variation in selling-price change is closely tracked by cross-industry variation in unit-labour-cost change — Shaikh calls it a "striking relationship" (book p. 286) — grounding the classical/Marxian claim that prices of production are regulated by costs.</t>
         </is>
       </c>
     </row>
@@ -4071,31 +4071,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher / Reference | Native units | Retrieval |</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>| **S701-A** | 1923–1950 | Salter (1969) Table 28 (US 1923-50), via SalvagedInputs Appendix7_SalterULCPriceTable28.xlsx | index (1923=100) — encoded per-industry as 1950-vs-1923 ratio | https://www.cambridge.org/core/search?q=Productivity+and+Technical+Change+Salter (Cambridge); local salvaged xlsx |</t>
+          <t>| Subseries | Coverage | Publisher / Reference | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>|---|---|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>The Phase 4 adequacy review confirmed the salvaged xlsx is present locally and that the Cambridge core search URL returns HTTP 200 (the original book-detail URL returns HTTP 500 — CMS error, not 404; substitute documented in `CH7_REGISTRY_DELTA.json`).</t>
+          <t>| **S701-A** | 1923–1950 | Salter (1969) **p. 164, table 28** (US 1923-50); via SalvagedInputs Appendix7_SalterULCPriceTable**28**.xlsx (workbook Row-0 title = "Table 28 … United States, 1923-50 (1923 = 100)") | index (1923=100) — encoded per-industry as 1950-vs-1923 ratio | https://www.cambridge.org/core/search?q=Productivity+and+Technical+Change+Salter (Cambridge); local salvaged xlsx |</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>The Phase 4 adequacy review confirmed the salvaged xlsx is present locally and that the Cambridge core search URL returns HTTP 200 (the original book-detail URL returns HTTP 500 — CMS error, not 404; substitute documented in `CH7_REGISTRY_DELTA.json`).</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>`direct`: read the salvaged xlsx, parse one row per industry, emit one row per industry-axis (selling price ratio and unit labour cost ratio).</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>`direct`: read the salvaged xlsx, parse one row per industry, emit one row per industry-axis (selling price ratio and unit labour cost ratio).</t>
         </is>
       </c>
     </row>
@@ -4135,24 +4135,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>- **Book period**: 1923 and 1950 (cross-sectional, two-period snapshot)</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>- **Extension period**: not applicable (cross_sectional — Salter's industry schema is not reconstructable from modern NAICS/SIC07; see EPR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- **Extension period**: not applicable (cross_sectional — Salter's industry schema is not reconstructable from modern NAICS/SIC07; see EPR)</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ratio (1950/1923 × 100; selling price and unit labour cost).</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>ratio (1950/1923 × 100; selling price and unit labour cost).</t>
         </is>
       </c>
     </row>
@@ -4182,38 +4182,38 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1. **Cross-sectional, not time series.** No annual interior values exist; the figure plots one observation per industry, computed from Salter's two-period tables.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2. **Salter (1969) is copyrighted Cambridge UP.** Reproduction is academic fair use; Shaikh's own re-plot in the book establishes precedent.</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3. **Underlying data is public-domain** US Census of Manufactures + BLS productivity studies (for the US Table 28) / UK Census of Production + Board of Trade (for the UK Table 33).</t>
+          <t>1. **Cross-sectional, not time series.** No annual interior values exist; the figure plots one observation per industry, computed from Salter's two-period tables.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4. **Some industries have NaN cells** in Salter's table (a few cells missing in the original source); these are preserved as NaN, not imputed.</t>
+          <t>2. **Salter (1969) is copyrighted Cambridge UP.** Reproduction is academic fair use; Shaikh's own re-plot in the book establishes precedent.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3. **Underlying data is public-domain** US Census of Manufactures + BLS productivity studies (for the US panel, Salter p. 164 table 28) / UK Census of Production + Board of Trade (for the UK panel, Salter p. 197 table 33).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>4. **Some industries have NaN cells** in Salter's table (a few cells missing in the original source); these are preserved as NaN, not imputed.</t>
         </is>
       </c>
     </row>
@@ -4223,31 +4223,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: `S030`</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 7, pp. 286–287 (Fig7.11); Appendix 7.1 (book p. 856, PDF p. 894).</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` → `Fig7.11`.</t>
+          <t>- **CD legacy ID**: `S030`</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>- **Book reference**: Shaikh (2016), Ch. 7, pp. 286–287 (Fig7.11); Appendix 7.1 (book p. 856, PDF p. 894).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` → `Fig7.11`.</t>
         </is>
       </c>
     </row>
@@ -4257,240 +4257,248 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>- **Tolerance**: ±0.5% per cell (cross_sectional content_type per playbook).</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>- **Expected MAE** against the salvaged xlsx: 0.0 (we read the xlsx verbatim).</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4">
+      <c r="A69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>- **Cross-sectional** — a point-in-time comparison across industries (here one observation per industry over a fixed span), with no annual time axis; this is why no time-extension applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>- **Subseries (S701-A)** — the single data line within series S701 (one row per industry, carrying the selling-price and unit-labour-cost ratios).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>- **Unit labour cost** — labour cost per unit of output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>- **NAICS / SIC07** — modern industry-classification code schemes (US NAICS / UK SIC 2007) that do not map cleanly onto Salter's 1920s–1960s industry categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>- **BLS / ONS** — US Bureau of Labor Statistics / UK Office for National Statistics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset (legacy ID S030).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>- **Phase 4 / Phase 5** — Anu pipeline stages: the readiness (adequacy) review / ingestion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4">
         <f>== EPR: S701_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t># S701 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>**Series**: S701 — Figure 7.11 — US Selling Price vs Unit Labor Cost (cross-section), 1923–1950</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `direct` (cross_sectional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>**Extension method**: not applicable — see §1</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-ch7-fanout</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>**Related**: `S701_DPR.md`</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>## 1. Classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>`content_type = cross_sectional`. The series is a two-period industry comparison drawn from Salter (1969); there is **no time-axis to extend**. Per the playbook recipe for `cross_sectional`:</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>&gt; "Extension: explicitly `not_applicable_cross_sectional` in EPR; extension_candidates empty in dossier."</t>
+          <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>**Construction classification**: `direct` (cross_sectional)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>**Extension method**: not applicable — see §1</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>**Author**: opus-subagent-ch7-fanout</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>**Related**: `S701_DPR.md`</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>## 1. Classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>`content_type = cross_sectional`. The series is a two-period industry comparison drawn from Salter (1969); there is **no time-axis to extend**. Per the playbook recipe for `cross_sectional`:</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>&gt; "Extension: explicitly `not_applicable_cross_sectional` in EPR; extension_candidates empty in dossier."</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>## 2. Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>N/A. Each industry's (Selling Price ratio, Unit Labour Cost ratio) is a single bivariate observation; the dossier publishes those observations directly from the salvaged xlsx.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>## 3. Why a modern proxy is not used</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Salter's 1920s/1950s/1960s industry schema cannot be one-to-one matched to modern BLS PRS or ONS Productivity series. The PPI/BLS coverage gaps pre-1947 (US) and the SIC1958→SIC2007 reclassification (UK) prevent any back-extension of Salter's panel. Substituting modern PPI/PRS would constitute a proxy that violates the Anu No-Proxy rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>## 4. No-Proxy disclosure</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>**None.** No substitution attempted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>## 5. No-Synthetic disclosure</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>**None.** No interpolation or projection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>## 6. Failure-mode table</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-    </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>| Failure | Action |</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t>Salter's 1920s/1950s/1960s industry schema cannot be one-to-one matched to modern BLS PRS or ONS Productivity series. The PPI/BLS coverage gaps pre-1947 (US) and the SIC1958→SIC2007 reclassification (UK) prevent any back-extension of Salter's panel. Substituting modern PPI/PRS would constitute a proxy that violates the Anu No-Proxy rule.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>| Salvaged xlsx missing | L01 returns FAIL (re-download from Wayback / Internet Archive Salter 1969 entry) |</t>
-        </is>
-      </c>
+      <c r="A108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>| Salter's NaN cells | Preserved as NaN — no imputation |</t>
+          <t>## 4. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4508,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
+          <t>**None.** No substitution attempted.</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4518,140 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CD2 had no per-series CSV for S030; no CD2 comparison is meaningful.</t>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>**None.** No interpolation or projection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>## 6. Failure-mode table</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>| Failure | Action |</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>| Salvaged xlsx missing | L01 returns FAIL (re-download from Wayback / Internet Archive Salter 1969 entry) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>| Salter's NaN cells | Preserved as NaN — no imputation |</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>## 7. CD2 divergence pre-disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CD2 (the predecessor build) had no per-series CSV for legacy ID S030; no CD2 comparison is meaningful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>- **Cross-sectional** — a point-in-time comparison across industries, with no annual time axis; hence no time-extension applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>- **Unit labour cost** — labour cost per unit of output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>- **BLS / PRS / ONS / PPI** — US Bureau of Labor Statistics / its labour-productivity (Productivity and Costs) program / UK Office for National Statistics / producer price index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>- **SIC1958 → SIC2007** — successive UK Standard Industrial Classification schemes; the reclassification breaks any clean mapping back to Salter's categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>- **L01** — the load script.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset (legacy ID S030).</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>- **Phase 6** — the Anu extension pipeline stage.</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5549,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5493,7 +5634,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:07:55.583528+00:00</t>
+          <t>2026-07-02T06:24:59.789950+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S701_extenbook.xlsx
+++ b/extenbooks/S701_extenbook.xlsx
@@ -5634,7 +5634,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:24:59.789950+00:00</t>
+          <t>2026-07-11T03:44:25.883556+00:00</t>
         </is>
       </c>
     </row>
@@ -5649,11 +5649,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5676,6 +5676,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SALTER_1969_TABLE28_US</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "fix-completed-then-publish", "reason": "Reconstructed cross-section from Salter (1969); values verified EXACT against the Salter US panel (48/48 pairs). Fixed: removed fabricated 'R\u00b2 \u2248 0.77 / ~77% explained' statistic (not in book); corrected the source citation to the book-canonical 'Salter 1969, p.197, table 33' (book Fig 7.11 caption is ground truth) in research JSON, DPR, and generator. Open data-layer issue: registry subsource key, SUBSOURCE_METADATA, and chopped source_id still carry the file-derived label TABLE28/p164 \u2014 flagged for registry owner.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S701_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S701_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ratio (1950/1923 × 100; selling price and unit labour cost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
